--- a/gstdatabase/GSTR-3B-2018-2019.xlsx
+++ b/gstdatabase/GSTR-3B-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B90B1E5-C6D1-4A70-86E8-27267A5D1F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D962C-57BE-4627-8226-13CBF92D3EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="BH12" s="10">
         <f t="shared" si="22"/>
-        <v>99764</v>
+        <v>99765</v>
       </c>
       <c r="BI12" s="7">
-        <v>280710</v>
+        <v>280711</v>
       </c>
       <c r="BJ12" s="9">
         <f t="shared" si="23"/>
-        <v>0.92709960598844721</v>
+        <v>0.92710290868377687</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="AX15" s="10">
         <f t="shared" si="18"/>
-        <v>131230</v>
+        <v>131231</v>
       </c>
       <c r="AY15" s="7">
-        <v>369544</v>
+        <v>369545</v>
       </c>
       <c r="AZ15" s="9">
         <f t="shared" si="19"/>
-        <v>0.88266387050390638</v>
+        <v>0.88266625902562645</v>
       </c>
       <c r="BA15" s="6">
         <v>419885</v>
@@ -2333,14 +2333,14 @@
       </c>
       <c r="BC15" s="10">
         <f t="shared" si="20"/>
-        <v>76790</v>
+        <v>76791</v>
       </c>
       <c r="BD15" s="7">
-        <v>372070</v>
+        <v>372071</v>
       </c>
       <c r="BE15" s="9">
         <f t="shared" si="21"/>
-        <v>0.88612358145682746</v>
+        <v>0.88612596306131441</v>
       </c>
       <c r="BF15" s="6">
         <v>421476</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="BH15" s="10">
         <f t="shared" si="22"/>
-        <v>147801</v>
+        <v>147802</v>
       </c>
       <c r="BI15" s="7">
-        <v>374872</v>
+        <v>374873</v>
       </c>
       <c r="BJ15" s="9">
         <f t="shared" si="23"/>
-        <v>0.88942668147178017</v>
+        <v>0.88942905408611639</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2587,14 +2587,14 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" si="0"/>
-        <v>242315</v>
+        <v>242316</v>
       </c>
       <c r="F17" s="7">
-        <v>439553</v>
+        <v>439554</v>
       </c>
       <c r="G17" s="9">
         <f t="shared" si="1"/>
-        <v>0.93721521794289542</v>
+        <v>0.93721735014360374</v>
       </c>
       <c r="H17" s="4">
         <v>489282</v>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="AI17" s="10">
         <f t="shared" si="12"/>
-        <v>143340</v>
+        <v>143342</v>
       </c>
       <c r="AJ17" s="7">
-        <v>474890</v>
+        <v>474892</v>
       </c>
       <c r="AK17" s="9">
         <f t="shared" si="13"/>
-        <v>0.91275149725918925</v>
+        <v>0.91275534131359026</v>
       </c>
       <c r="AL17" s="4">
         <v>524911</v>
@@ -2706,14 +2706,14 @@
       </c>
       <c r="AN17" s="10">
         <f t="shared" si="14"/>
-        <v>119146</v>
+        <v>119148</v>
       </c>
       <c r="AO17" s="7">
-        <v>474447</v>
+        <v>474449</v>
       </c>
       <c r="AP17" s="9">
         <f t="shared" si="15"/>
-        <v>0.90386179752377072</v>
+        <v>0.90386560769349467</v>
       </c>
       <c r="AQ17" s="4">
         <v>530594</v>
@@ -2723,14 +2723,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>127503</v>
+        <v>127505</v>
       </c>
       <c r="AT17" s="7">
-        <v>478900</v>
+        <v>478902</v>
       </c>
       <c r="AU17" s="9">
         <f t="shared" si="17"/>
-        <v>0.90257334232954012</v>
+        <v>0.90257711168991739</v>
       </c>
       <c r="AV17" s="6">
         <v>538347</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>162551</v>
+        <v>162552</v>
       </c>
       <c r="AY17" s="7">
-        <v>483874</v>
+        <v>483875</v>
       </c>
       <c r="AZ17" s="9">
         <f t="shared" si="19"/>
-        <v>0.89881433350608442</v>
+        <v>0.8988161910440664</v>
       </c>
       <c r="BA17" s="6">
         <v>545177</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>100825</v>
+        <v>100826</v>
       </c>
       <c r="BD17" s="7">
-        <v>489110</v>
+        <v>489111</v>
       </c>
       <c r="BE17" s="9">
         <f t="shared" si="21"/>
-        <v>0.89715817064916537</v>
+        <v>0.8971600049158347</v>
       </c>
       <c r="BF17" s="6">
         <v>551432</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>209690</v>
+        <v>209691</v>
       </c>
       <c r="BI17" s="7">
-        <v>493405</v>
+        <v>493406</v>
       </c>
       <c r="BJ17" s="9">
         <f t="shared" si="23"/>
-        <v>0.89477034339682859</v>
+        <v>0.8947721568570558</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>416759</v>
+        <v>416760</v>
       </c>
       <c r="F18" s="7">
-        <v>867168</v>
+        <v>867169</v>
       </c>
       <c r="G18" s="9">
         <f t="shared" si="1"/>
-        <v>0.91998820266797932</v>
+        <v>0.91998926357913235</v>
       </c>
       <c r="H18" s="4">
         <v>980551</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>214881</v>
+        <v>214882</v>
       </c>
       <c r="K18" s="7">
-        <v>889304</v>
+        <v>889305</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="3"/>
-        <v>0.90694313707293139</v>
+        <v>0.90694415690769781</v>
       </c>
       <c r="M18" s="4">
         <v>1006440</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>222986</v>
+        <v>222987</v>
       </c>
       <c r="P18" s="7">
-        <v>903686</v>
+        <v>903687</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="5"/>
-        <v>0.89790350145065778</v>
+        <v>0.89790449505186598</v>
       </c>
       <c r="R18" s="4">
         <v>1025384</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>174920</v>
+        <v>174921</v>
       </c>
       <c r="U18" s="7">
-        <v>917018</v>
+        <v>917019</v>
       </c>
       <c r="V18" s="9">
         <f t="shared" si="7"/>
-        <v>0.89431666575643853</v>
+        <v>0.89431764100083477</v>
       </c>
       <c r="W18" s="4">
         <v>1044299</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>254596</v>
+        <v>254597</v>
       </c>
       <c r="Z18" s="7">
-        <v>930887</v>
+        <v>930888</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="9"/>
-        <v>0.89139891927503523</v>
+        <v>0.89139987685519184</v>
       </c>
       <c r="AB18" s="4">
         <v>1050898</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>187477</v>
+        <v>187478</v>
       </c>
       <c r="AE18" s="7">
-        <v>943114</v>
+        <v>943115</v>
       </c>
       <c r="AF18" s="9">
         <f t="shared" si="11"/>
-        <v>0.89743628782241469</v>
+        <v>0.89743723938955067</v>
       </c>
       <c r="AG18" s="4">
         <v>1062525</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>256113</v>
+        <v>256114</v>
       </c>
       <c r="AJ18" s="7">
-        <v>957862</v>
+        <v>957863</v>
       </c>
       <c r="AK18" s="9">
         <f t="shared" si="13"/>
-        <v>0.90149596480082816</v>
+        <v>0.90149690595515397</v>
       </c>
       <c r="AL18" s="4">
         <v>1073550</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>218727</v>
+        <v>218728</v>
       </c>
       <c r="AO18" s="7">
-        <v>956530</v>
+        <v>956531</v>
       </c>
       <c r="AP18" s="9">
         <f t="shared" si="15"/>
-        <v>0.89099715895859533</v>
+        <v>0.89099809044758049</v>
       </c>
       <c r="AQ18" s="4">
         <v>1080975</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>233202</v>
+        <v>233203</v>
       </c>
       <c r="AT18" s="7">
-        <v>967316</v>
+        <v>967317</v>
       </c>
       <c r="AU18" s="9">
         <f t="shared" si="17"/>
-        <v>0.89485510765743892</v>
+        <v>0.89485603274821346</v>
       </c>
       <c r="AV18" s="6">
         <v>1090269</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="18"/>
-        <v>321389</v>
+        <v>321390</v>
       </c>
       <c r="AY18" s="7">
-        <v>975596</v>
+        <v>975597</v>
       </c>
       <c r="AZ18" s="9">
         <f t="shared" si="19"/>
-        <v>0.89482136977204707</v>
+        <v>0.89482228697688371</v>
       </c>
       <c r="BA18" s="6">
         <v>1099973</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>196059</v>
+        <v>196060</v>
       </c>
       <c r="BD18" s="7">
-        <v>982912</v>
+        <v>982913</v>
       </c>
       <c r="BE18" s="9">
         <f t="shared" si="21"/>
-        <v>0.89357829692183355</v>
+        <v>0.89357920603505725</v>
       </c>
       <c r="BF18" s="6">
         <v>1108438</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>378211</v>
+        <v>378212</v>
       </c>
       <c r="BI18" s="7">
-        <v>990077</v>
+        <v>990078</v>
       </c>
       <c r="BJ18" s="9">
         <f t="shared" si="23"/>
-        <v>0.89321820435603971</v>
+        <v>0.8932191065264814</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>59012</v>
+        <v>59013</v>
       </c>
       <c r="AY27" s="7">
-        <v>118342</v>
+        <v>118343</v>
       </c>
       <c r="AZ27" s="9">
         <f t="shared" si="19"/>
-        <v>0.77428683590683067</v>
+        <v>0.77429337869667625</v>
       </c>
       <c r="BA27" s="6">
         <v>154902</v>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>73061</v>
+        <v>73062</v>
       </c>
       <c r="BI27" s="7">
-        <v>120364</v>
+        <v>120365</v>
       </c>
       <c r="BJ27" s="9">
         <f t="shared" si="23"/>
-        <v>0.76546004935005474</v>
+        <v>0.76546640889318507</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="O28" s="10">
         <f t="shared" si="4"/>
-        <v>135597</v>
+        <v>135598</v>
       </c>
       <c r="P28" s="7">
-        <v>468468</v>
+        <v>468469</v>
       </c>
       <c r="Q28" s="9">
         <f t="shared" si="5"/>
-        <v>0.91586738663778444</v>
+        <v>0.91586934166435319</v>
       </c>
       <c r="R28" s="4">
         <v>521022</v>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="18"/>
-        <v>164925</v>
+        <v>164926</v>
       </c>
       <c r="AY28" s="7">
-        <v>508405</v>
+        <v>508406</v>
       </c>
       <c r="AZ28" s="9">
         <f t="shared" si="19"/>
-        <v>0.89474369646593799</v>
+        <v>0.89474545636935443</v>
       </c>
       <c r="BA28" s="6">
         <v>575661</v>
@@ -5089,14 +5089,14 @@
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="20"/>
-        <v>113641</v>
+        <v>113642</v>
       </c>
       <c r="BD28" s="7">
-        <v>513685</v>
+        <v>513686</v>
       </c>
       <c r="BE28" s="9">
         <f t="shared" si="21"/>
-        <v>0.89233941503766978</v>
+        <v>0.89234115217115628</v>
       </c>
       <c r="BF28" s="6">
         <v>582519</v>
@@ -5479,14 +5479,14 @@
       </c>
       <c r="AS30" s="10">
         <f t="shared" si="16"/>
-        <v>61520</v>
+        <v>61521</v>
       </c>
       <c r="AT30" s="7">
-        <v>188422</v>
+        <v>188423</v>
       </c>
       <c r="AU30" s="9">
         <f t="shared" si="17"/>
-        <v>0.84440779596757209</v>
+        <v>0.84441227743892877</v>
       </c>
       <c r="AV30" s="6">
         <v>220757</v>
@@ -5496,14 +5496,14 @@
       </c>
       <c r="AX30" s="10">
         <f t="shared" si="18"/>
-        <v>71363</v>
+        <v>71364</v>
       </c>
       <c r="AY30" s="7">
-        <v>190720</v>
+        <v>190721</v>
       </c>
       <c r="AZ30" s="9">
         <f t="shared" si="19"/>
-        <v>0.86393636441879529</v>
+        <v>0.86394089428647791</v>
       </c>
       <c r="BA30" s="6">
         <v>218783</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="BC30" s="10">
         <f t="shared" si="20"/>
-        <v>49132</v>
+        <v>49133</v>
       </c>
       <c r="BD30" s="7">
-        <v>192493</v>
+        <v>192494</v>
       </c>
       <c r="BE30" s="9">
         <f t="shared" si="21"/>
-        <v>0.87983527056489763</v>
+        <v>0.87983984130394044</v>
       </c>
       <c r="BF30" s="6">
         <v>218115</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="BH30" s="10">
         <f t="shared" si="22"/>
-        <v>82462</v>
+        <v>82463</v>
       </c>
       <c r="BI30" s="7">
-        <v>193889</v>
+        <v>193890</v>
       </c>
       <c r="BJ30" s="9">
         <f t="shared" si="23"/>
-        <v>0.88893015152557142</v>
+        <v>0.88893473626298058</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5979,14 +5979,14 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="0"/>
-        <v>401555</v>
+        <v>401558</v>
       </c>
       <c r="F33" s="7">
-        <v>722983</v>
+        <v>722986</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="1"/>
-        <v>0.94660151590733821</v>
+        <v>0.94660544380681544</v>
       </c>
       <c r="H33" s="4">
         <v>790674</v>
@@ -5996,14 +5996,14 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v>169979</v>
+        <v>169981</v>
       </c>
       <c r="K33" s="7">
-        <v>735197</v>
+        <v>735199</v>
       </c>
       <c r="L33" s="9">
         <f t="shared" si="3"/>
-        <v>0.92983581096634016</v>
+        <v>0.92983834045384062</v>
       </c>
       <c r="M33" s="4">
         <v>801034</v>
@@ -6013,14 +6013,14 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="4"/>
-        <v>180422</v>
+        <v>180424</v>
       </c>
       <c r="P33" s="7">
-        <v>744299</v>
+        <v>744301</v>
       </c>
       <c r="Q33" s="9">
         <f t="shared" si="5"/>
-        <v>0.92917279416354359</v>
+        <v>0.92917529093646467</v>
       </c>
       <c r="R33" s="4">
         <v>811485</v>
@@ -6030,14 +6030,14 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="6"/>
-        <v>138454</v>
+        <v>138456</v>
       </c>
       <c r="U33" s="7">
-        <v>751891</v>
+        <v>751893</v>
       </c>
       <c r="V33" s="9">
         <f t="shared" si="7"/>
-        <v>0.92656179719896237</v>
+        <v>0.92656426181629969</v>
       </c>
       <c r="W33" s="4">
         <v>819064</v>
@@ -6047,14 +6047,14 @@
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="8"/>
-        <v>204483</v>
+        <v>204484</v>
       </c>
       <c r="Z33" s="7">
-        <v>761134</v>
+        <v>761135</v>
       </c>
       <c r="AA33" s="9">
         <f t="shared" si="9"/>
-        <v>0.92927292616938362</v>
+        <v>0.92927414707519806</v>
       </c>
       <c r="AB33" s="4">
         <v>823883</v>
@@ -6064,14 +6064,14 @@
       </c>
       <c r="AD33" s="10">
         <f t="shared" si="10"/>
-        <v>153445</v>
+        <v>153446</v>
       </c>
       <c r="AE33" s="7">
-        <v>767921</v>
+        <v>767922</v>
       </c>
       <c r="AF33" s="9">
         <f t="shared" si="11"/>
-        <v>0.9320753068093407</v>
+        <v>0.93207652057391643</v>
       </c>
       <c r="AG33" s="4">
         <v>827687</v>
@@ -6081,14 +6081,14 @@
       </c>
       <c r="AI33" s="10">
         <f t="shared" si="12"/>
-        <v>226204</v>
+        <v>226206</v>
       </c>
       <c r="AJ33" s="7">
-        <v>773754</v>
+        <v>773756</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="13"/>
-        <v>0.93483889441298462</v>
+        <v>0.93484131078535726</v>
       </c>
       <c r="AL33" s="4">
         <v>833066</v>
@@ -6098,14 +6098,14 @@
       </c>
       <c r="AN33" s="10">
         <f t="shared" si="14"/>
-        <v>170650</v>
+        <v>170652</v>
       </c>
       <c r="AO33" s="7">
-        <v>774389</v>
+        <v>774391</v>
       </c>
       <c r="AP33" s="9">
         <f t="shared" si="15"/>
-        <v>0.92956500445342871</v>
+        <v>0.92956740522359571</v>
       </c>
       <c r="AQ33" s="4">
         <v>838229</v>
@@ -6115,14 +6115,14 @@
       </c>
       <c r="AS33" s="10">
         <f t="shared" si="16"/>
-        <v>188063</v>
+        <v>188065</v>
       </c>
       <c r="AT33" s="7">
-        <v>782819</v>
+        <v>782821</v>
       </c>
       <c r="AU33" s="9">
         <f t="shared" si="17"/>
-        <v>0.93389634574799962</v>
+        <v>0.93389873173082771</v>
       </c>
       <c r="AV33" s="6">
         <v>846900</v>
@@ -6132,14 +6132,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>217583</v>
+        <v>217586</v>
       </c>
       <c r="AY33" s="7">
-        <v>788691</v>
+        <v>788694</v>
       </c>
       <c r="AZ33" s="9">
         <f t="shared" si="19"/>
-        <v>0.93126815444562527</v>
+        <v>0.93127169677647892</v>
       </c>
       <c r="BA33" s="6">
         <v>854421</v>
@@ -6149,14 +6149,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>134198</v>
+        <v>134202</v>
       </c>
       <c r="BD33" s="7">
-        <v>795545</v>
+        <v>795549</v>
       </c>
       <c r="BE33" s="9">
         <f t="shared" si="21"/>
-        <v>0.93109251762304535</v>
+        <v>0.9310971991559196</v>
       </c>
       <c r="BF33" s="6">
         <v>864165</v>
@@ -6166,14 +6166,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>281128</v>
+        <v>281131</v>
       </c>
       <c r="BI33" s="7">
-        <v>802669</v>
+        <v>802672</v>
       </c>
       <c r="BJ33" s="9">
         <f t="shared" si="23"/>
-        <v>0.92883766410349877</v>
+        <v>0.92884113566274962</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6615,14 +6615,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>635206</v>
+        <v>635207</v>
       </c>
       <c r="F36" s="7">
-        <v>1117307</v>
+        <v>1117308</v>
       </c>
       <c r="G36" s="9">
         <f t="shared" si="1"/>
-        <v>0.90621801329187124</v>
+        <v>0.90621882436529444</v>
       </c>
       <c r="H36" s="4">
         <v>1268548</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>364151</v>
+        <v>364152</v>
       </c>
       <c r="K36" s="7">
-        <v>1135869</v>
+        <v>1135870</v>
       </c>
       <c r="L36" s="9">
         <f t="shared" si="3"/>
-        <v>0.89540876655830126</v>
+        <v>0.89540955486114837</v>
       </c>
       <c r="M36" s="4">
         <v>1291465</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>366231</v>
+        <v>366232</v>
       </c>
       <c r="P36" s="7">
-        <v>1150173</v>
+        <v>1150174</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="5"/>
-        <v>0.89059556395256545</v>
+        <v>0.8905963382670069</v>
       </c>
       <c r="R36" s="4">
         <v>1304709</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>409287</v>
+        <v>409288</v>
       </c>
       <c r="AJ36" s="7">
-        <v>1192847</v>
+        <v>1192848</v>
       </c>
       <c r="AK36" s="9">
         <f t="shared" si="13"/>
-        <v>0.89230054562237904</v>
+        <v>0.89230129366512523</v>
       </c>
       <c r="AL36" s="4">
         <v>1349209</v>
@@ -6785,14 +6785,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>293546</v>
+        <v>293547</v>
       </c>
       <c r="BD36" s="7">
-        <v>1221221</v>
+        <v>1221222</v>
       </c>
       <c r="BE36" s="9">
         <f t="shared" si="21"/>
-        <v>0.89522355280056765</v>
+        <v>0.8952242858567081</v>
       </c>
       <c r="BF36" s="6">
         <v>1384075</v>
@@ -6802,14 +6802,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="22"/>
-        <v>511479</v>
+        <v>511480</v>
       </c>
       <c r="BI36" s="7">
-        <v>1229541</v>
+        <v>1229542</v>
       </c>
       <c r="BJ36" s="9">
         <f t="shared" si="23"/>
-        <v>0.88834853602586561</v>
+        <v>0.88834925853006519</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6827,14 +6827,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>356718</v>
+        <v>356719</v>
       </c>
       <c r="F37" s="7">
-        <v>552285</v>
+        <v>552286</v>
       </c>
       <c r="G37" s="9">
         <f t="shared" si="1"/>
-        <v>0.89441039053580251</v>
+        <v>0.89441201000834025</v>
       </c>
       <c r="H37" s="4">
         <v>636289</v>
@@ -6861,14 +6861,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>166955</v>
+        <v>166957</v>
       </c>
       <c r="P37" s="7">
-        <v>569070</v>
+        <v>569072</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="5"/>
-        <v>0.87487585670404544</v>
+        <v>0.87487893146060158</v>
       </c>
       <c r="R37" s="4">
         <v>663657</v>
@@ -6929,14 +6929,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>185430</v>
+        <v>185432</v>
       </c>
       <c r="AJ37" s="7">
-        <v>603113</v>
+        <v>603115</v>
       </c>
       <c r="AK37" s="9">
         <f t="shared" si="13"/>
-        <v>0.87173449889716614</v>
+        <v>0.87173738968048176</v>
       </c>
       <c r="AL37" s="4">
         <v>698331</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>163066</v>
+        <v>163070</v>
       </c>
       <c r="AO37" s="7">
-        <v>603945</v>
+        <v>603949</v>
       </c>
       <c r="AP37" s="9">
         <f t="shared" si="15"/>
-        <v>0.86484059851273964</v>
+        <v>0.86484632645550608</v>
       </c>
       <c r="AQ37" s="4">
         <v>700400</v>
@@ -6963,14 +6963,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>175163</v>
+        <v>175167</v>
       </c>
       <c r="AT37" s="7">
-        <v>611992</v>
+        <v>611996</v>
       </c>
       <c r="AU37" s="9">
         <f t="shared" si="17"/>
-        <v>0.87377498572244428</v>
+        <v>0.87378069674471726</v>
       </c>
       <c r="AV37" s="6">
         <v>698615</v>
@@ -6980,14 +6980,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>212639</v>
+        <v>212643</v>
       </c>
       <c r="AY37" s="7">
-        <v>619452</v>
+        <v>619456</v>
       </c>
       <c r="AZ37" s="9">
         <f t="shared" si="19"/>
-        <v>0.88668579976095563</v>
+        <v>0.88669152537520668</v>
       </c>
       <c r="BA37" s="6">
         <v>701194</v>
@@ -6997,14 +6997,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>123324</v>
+        <v>123327</v>
       </c>
       <c r="BD37" s="7">
-        <v>626360</v>
+        <v>626363</v>
       </c>
       <c r="BE37" s="9">
         <f t="shared" si="21"/>
-        <v>0.89327632580997551</v>
+        <v>0.89328060422650513</v>
       </c>
       <c r="BF37" s="6">
         <v>706472</v>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="22"/>
-        <v>257262</v>
+        <v>257267</v>
       </c>
       <c r="BI37" s="7">
-        <v>632161</v>
+        <v>632166</v>
       </c>
       <c r="BJ37" s="9">
         <f t="shared" si="23"/>
-        <v>0.89481394874814568</v>
+        <v>0.89482102616947312</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7463,14 +7463,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="0"/>
-        <v>154111</v>
+        <v>154112</v>
       </c>
       <c r="F40" s="7">
-        <v>239016</v>
+        <v>239017</v>
       </c>
       <c r="G40" s="9">
         <f t="shared" si="1"/>
-        <v>0.94790067934944255</v>
+        <v>0.94790464519557571</v>
       </c>
       <c r="H40" s="4">
         <v>258924</v>
@@ -7480,14 +7480,14 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="2"/>
-        <v>92853</v>
+        <v>92854</v>
       </c>
       <c r="K40" s="7">
-        <v>243227</v>
+        <v>243228</v>
       </c>
       <c r="L40" s="9">
         <f t="shared" si="3"/>
-        <v>0.93937603312168827</v>
+        <v>0.93937989525884047</v>
       </c>
       <c r="M40" s="4">
         <v>263762</v>
@@ -7497,14 +7497,14 @@
       </c>
       <c r="O40" s="10">
         <f t="shared" si="4"/>
-        <v>95393</v>
+        <v>95394</v>
       </c>
       <c r="P40" s="7">
-        <v>246295</v>
+        <v>246296</v>
       </c>
       <c r="Q40" s="9">
         <f t="shared" si="5"/>
-        <v>0.93377742055337765</v>
+        <v>0.93378121185007701</v>
       </c>
       <c r="R40" s="4">
         <v>267922</v>
@@ -7514,14 +7514,14 @@
       </c>
       <c r="T40" s="10">
         <f t="shared" si="6"/>
-        <v>102651</v>
+        <v>102652</v>
       </c>
       <c r="U40" s="7">
-        <v>249615</v>
+        <v>249616</v>
       </c>
       <c r="V40" s="9">
         <f t="shared" si="7"/>
-        <v>0.93167041153768637</v>
+        <v>0.9316741439672741</v>
       </c>
       <c r="W40" s="4">
         <v>271146</v>
@@ -7531,14 +7531,14 @@
       </c>
       <c r="Y40" s="10">
         <f t="shared" si="8"/>
-        <v>145068</v>
+        <v>145069</v>
       </c>
       <c r="Z40" s="7">
-        <v>252201</v>
+        <v>252202</v>
       </c>
       <c r="AA40" s="9">
         <f t="shared" si="9"/>
-        <v>0.93012989312031158</v>
+        <v>0.93013358117029199</v>
       </c>
       <c r="AB40" s="4">
         <v>273181</v>
@@ -7548,14 +7548,14 @@
       </c>
       <c r="AD40" s="10">
         <f t="shared" si="10"/>
-        <v>87407</v>
+        <v>87408</v>
       </c>
       <c r="AE40" s="7">
-        <v>254742</v>
+        <v>254743</v>
       </c>
       <c r="AF40" s="9">
         <f t="shared" si="11"/>
-        <v>0.93250262646377313</v>
+        <v>0.93250628704046035</v>
       </c>
       <c r="AG40" s="4">
         <v>276472</v>
@@ -7565,14 +7565,14 @@
       </c>
       <c r="AI40" s="10">
         <f t="shared" si="12"/>
-        <v>115262</v>
+        <v>115263</v>
       </c>
       <c r="AJ40" s="7">
-        <v>257308</v>
+        <v>257309</v>
       </c>
       <c r="AK40" s="9">
         <f t="shared" si="13"/>
-        <v>0.93068375821059635</v>
+        <v>0.93068737521340317</v>
       </c>
       <c r="AL40" s="4">
         <v>279758</v>
@@ -7582,14 +7582,14 @@
       </c>
       <c r="AN40" s="10">
         <f t="shared" si="14"/>
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="AO40" s="7">
-        <v>258712</v>
+        <v>258713</v>
       </c>
       <c r="AP40" s="9">
         <f t="shared" si="15"/>
-        <v>0.92477069467182349</v>
+        <v>0.92477426918979977</v>
       </c>
       <c r="AQ40" s="4">
         <v>281909</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="AS40" s="10">
         <f t="shared" si="16"/>
-        <v>102833</v>
+        <v>102834</v>
       </c>
       <c r="AT40" s="7">
-        <v>260823</v>
+        <v>260824</v>
       </c>
       <c r="AU40" s="9">
         <f t="shared" si="17"/>
-        <v>0.9252028136739161</v>
+        <v>0.92520636091788488</v>
       </c>
       <c r="AV40" s="6">
         <v>285037</v>
@@ -7616,14 +7616,14 @@
       </c>
       <c r="AX40" s="10">
         <f t="shared" si="18"/>
-        <v>119206</v>
+        <v>119207</v>
       </c>
       <c r="AY40" s="7">
-        <v>262797</v>
+        <v>262798</v>
       </c>
       <c r="AZ40" s="9">
         <f t="shared" si="19"/>
-        <v>0.92197504183667378</v>
+        <v>0.92197855015313801</v>
       </c>
       <c r="BA40" s="6">
         <v>287794</v>
@@ -7633,14 +7633,14 @@
       </c>
       <c r="BC40" s="10">
         <f t="shared" si="20"/>
-        <v>72080</v>
+        <v>72081</v>
       </c>
       <c r="BD40" s="7">
-        <v>264749</v>
+        <v>264750</v>
       </c>
       <c r="BE40" s="9">
         <f t="shared" si="21"/>
-        <v>0.91992536328067998</v>
+        <v>0.91992883798828329</v>
       </c>
       <c r="BF40" s="6">
         <v>291194</v>
@@ -7650,14 +7650,14 @@
       </c>
       <c r="BH40" s="10">
         <f t="shared" si="22"/>
-        <v>136549</v>
+        <v>136551</v>
       </c>
       <c r="BI40" s="7">
-        <v>267301</v>
+        <v>267303</v>
       </c>
       <c r="BJ40" s="9">
         <f t="shared" si="23"/>
-        <v>0.91794817200903867</v>
+        <v>0.91795504028242336</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>385862</v>
+        <v>385868</v>
       </c>
       <c r="F41" s="7">
-        <v>690948</v>
+        <v>690954</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="1"/>
-        <v>0.8504080050216003</v>
+        <v>0.85041538972787356</v>
       </c>
       <c r="H41" s="4">
         <v>835051</v>
@@ -7692,14 +7692,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>211154</v>
+        <v>211161</v>
       </c>
       <c r="K41" s="7">
-        <v>701674</v>
+        <v>701681</v>
       </c>
       <c r="L41" s="9">
         <f t="shared" si="3"/>
-        <v>0.84027682141569793</v>
+        <v>0.84028520413723229</v>
       </c>
       <c r="M41" s="4">
         <v>852643</v>
@@ -7709,14 +7709,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>211062</v>
+        <v>211066</v>
       </c>
       <c r="P41" s="7">
-        <v>709932</v>
+        <v>709936</v>
       </c>
       <c r="Q41" s="9">
         <f t="shared" si="5"/>
-        <v>0.83262514323110615</v>
+        <v>0.83262983452629058</v>
       </c>
       <c r="R41" s="4">
         <v>868359</v>
@@ -7726,14 +7726,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171939</v>
+        <v>171943</v>
       </c>
       <c r="U41" s="7">
-        <v>719486</v>
+        <v>719490</v>
       </c>
       <c r="V41" s="9">
         <f t="shared" si="7"/>
-        <v>0.82855823455506306</v>
+        <v>0.82856284094481658</v>
       </c>
       <c r="W41" s="4">
         <v>879806</v>
@@ -7743,14 +7743,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>230068</v>
+        <v>230073</v>
       </c>
       <c r="Z41" s="7">
-        <v>727727</v>
+        <v>727732</v>
       </c>
       <c r="AA41" s="9">
         <f t="shared" si="9"/>
-        <v>0.82714484784145592</v>
+        <v>0.82715053091249657</v>
       </c>
       <c r="AB41" s="4">
         <v>882248</v>
@@ -7760,14 +7760,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>187421</v>
+        <v>187425</v>
       </c>
       <c r="AE41" s="7">
-        <v>735484</v>
+        <v>735488</v>
       </c>
       <c r="AF41" s="9">
         <f t="shared" si="11"/>
-        <v>0.83364768183095905</v>
+        <v>0.83365221570352099</v>
       </c>
       <c r="AG41" s="4">
         <v>877145</v>
@@ -7777,14 +7777,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>242429</v>
+        <v>242433</v>
       </c>
       <c r="AJ41" s="7">
-        <v>743291</v>
+        <v>743295</v>
       </c>
       <c r="AK41" s="9">
         <f t="shared" si="13"/>
-        <v>0.84739809267566935</v>
+        <v>0.84740265292511496</v>
       </c>
       <c r="AL41" s="4">
         <v>875890</v>
@@ -7794,14 +7794,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>205254</v>
+        <v>205260</v>
       </c>
       <c r="AO41" s="7">
-        <v>742099</v>
+        <v>742105</v>
       </c>
       <c r="AP41" s="9">
         <f t="shared" si="15"/>
-        <v>0.8472513671808104</v>
+        <v>0.84725821735606066</v>
       </c>
       <c r="AQ41" s="4">
         <v>865402</v>
@@ -7811,14 +7811,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>247895</v>
+        <v>247901</v>
       </c>
       <c r="AT41" s="7">
-        <v>748363</v>
+        <v>748369</v>
       </c>
       <c r="AU41" s="9">
         <f t="shared" si="17"/>
-        <v>0.86475765020187145</v>
+        <v>0.86476458339592466</v>
       </c>
       <c r="AV41" s="6">
         <v>863602</v>
@@ -7828,14 +7828,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>252932</v>
+        <v>252940</v>
       </c>
       <c r="AY41" s="7">
-        <v>753210</v>
+        <v>753218</v>
       </c>
       <c r="AZ41" s="9">
         <f t="shared" si="19"/>
-        <v>0.87217259802547931</v>
+        <v>0.87218186155196487</v>
       </c>
       <c r="BA41" s="6">
         <v>853803</v>
@@ -7845,14 +7845,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>156266</v>
+        <v>156273</v>
       </c>
       <c r="BD41" s="7">
-        <v>760003</v>
+        <v>760010</v>
       </c>
       <c r="BE41" s="9">
         <f t="shared" si="21"/>
-        <v>0.89013859168918352</v>
+        <v>0.89014679030174404</v>
       </c>
       <c r="BF41" s="6">
         <v>867754</v>
@@ -7862,14 +7862,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="22"/>
-        <v>339130</v>
+        <v>339139</v>
       </c>
       <c r="BI41" s="7">
-        <v>767276</v>
+        <v>767285</v>
       </c>
       <c r="BJ41" s="9">
         <f t="shared" si="23"/>
-        <v>0.88420911917432821</v>
+        <v>0.88421949077734008</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8099,14 +8099,14 @@
       </c>
       <c r="E43" s="10">
         <f t="shared" si="0"/>
-        <v>2734</v>
+        <v>2736</v>
       </c>
       <c r="F43" s="7">
-        <v>3382</v>
+        <v>3384</v>
       </c>
       <c r="G43" s="9">
         <f t="shared" si="1"/>
-        <v>0.77285191956124311</v>
+        <v>0.77330895795246801</v>
       </c>
       <c r="H43" s="4">
         <v>4455</v>
@@ -8116,14 +8116,14 @@
       </c>
       <c r="J43" s="10">
         <f t="shared" si="2"/>
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="K43" s="7">
-        <v>3424</v>
+        <v>3426</v>
       </c>
       <c r="L43" s="9">
         <f t="shared" si="3"/>
-        <v>0.76857463524130187</v>
+        <v>0.76902356902356905</v>
       </c>
       <c r="M43" s="4">
         <v>4559</v>
@@ -8133,14 +8133,14 @@
       </c>
       <c r="O43" s="10">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="P43" s="7">
-        <v>3455</v>
+        <v>3457</v>
       </c>
       <c r="Q43" s="9">
         <f t="shared" si="5"/>
-        <v>0.7578416319368283</v>
+        <v>0.75828032463259487</v>
       </c>
       <c r="R43" s="4">
         <v>4602</v>
@@ -8150,14 +8150,14 @@
       </c>
       <c r="T43" s="10">
         <f t="shared" si="6"/>
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="U43" s="7">
-        <v>3470</v>
+        <v>3472</v>
       </c>
       <c r="V43" s="9">
         <f t="shared" si="7"/>
-        <v>0.75401999130812691</v>
+        <v>0.7544545849630595</v>
       </c>
       <c r="W43" s="4">
         <v>4626</v>
@@ -8167,14 +8167,14 @@
       </c>
       <c r="Y43" s="10">
         <f t="shared" si="8"/>
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="Z43" s="7">
-        <v>3491</v>
+        <v>3493</v>
       </c>
       <c r="AA43" s="9">
         <f t="shared" si="9"/>
-        <v>0.7546476437527021</v>
+        <v>0.75507998270644183</v>
       </c>
       <c r="AB43" s="4">
         <v>4663</v>
@@ -8184,14 +8184,14 @@
       </c>
       <c r="AD43" s="10">
         <f t="shared" si="10"/>
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="AE43" s="7">
-        <v>3511</v>
+        <v>3513</v>
       </c>
       <c r="AF43" s="9">
         <f t="shared" si="11"/>
-        <v>0.75294874544284796</v>
+        <v>0.75337765387089861</v>
       </c>
       <c r="AG43" s="4">
         <v>4719</v>
@@ -8201,14 +8201,14 @@
       </c>
       <c r="AI43" s="10">
         <f t="shared" si="12"/>
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="AJ43" s="7">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="AK43" s="9">
         <f t="shared" si="13"/>
-        <v>0.75015893197711381</v>
+        <v>0.75058275058275059</v>
       </c>
       <c r="AL43" s="4">
         <v>4722</v>
@@ -8218,14 +8218,14 @@
       </c>
       <c r="AN43" s="10">
         <f t="shared" si="14"/>
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="AO43" s="7">
-        <v>3493</v>
+        <v>3495</v>
       </c>
       <c r="AP43" s="9">
         <f t="shared" si="15"/>
-        <v>0.73972892842016091</v>
+        <v>0.74015247776365944</v>
       </c>
       <c r="AQ43" s="4">
         <v>4471</v>
@@ -8235,14 +8235,14 @@
       </c>
       <c r="AS43" s="10">
         <f t="shared" si="16"/>
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="AT43" s="7">
-        <v>3494</v>
+        <v>3496</v>
       </c>
       <c r="AU43" s="9">
         <f t="shared" si="17"/>
-        <v>0.78148065309774095</v>
+        <v>0.78192798031760236</v>
       </c>
       <c r="AV43" s="6">
         <v>4344</v>
@@ -8252,14 +8252,14 @@
       </c>
       <c r="AX43" s="10">
         <f t="shared" si="18"/>
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="AY43" s="7">
-        <v>3481</v>
+        <v>3483</v>
       </c>
       <c r="AZ43" s="9">
         <f t="shared" si="19"/>
-        <v>0.80133517495395945</v>
+        <v>0.80179558011049723</v>
       </c>
       <c r="BA43" s="6">
         <v>4029</v>
@@ -8269,14 +8269,14 @@
       </c>
       <c r="BC43" s="10">
         <f t="shared" si="20"/>
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="BD43" s="7">
-        <v>3461</v>
+        <v>3463</v>
       </c>
       <c r="BE43" s="9">
         <f t="shared" si="21"/>
-        <v>0.85902208984859763</v>
+        <v>0.85951849094068011</v>
       </c>
       <c r="BF43" s="6">
         <v>3923</v>
@@ -8286,14 +8286,14 @@
       </c>
       <c r="BH43" s="10">
         <f t="shared" si="22"/>
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="BI43" s="7">
-        <v>3445</v>
+        <v>3447</v>
       </c>
       <c r="BJ43" s="9">
         <f t="shared" si="23"/>
-        <v>0.87815447361712973</v>
+        <v>0.87866428753504966</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8430,14 +8430,14 @@
       </c>
       <c r="AN44" s="10">
         <f t="shared" si="14"/>
-        <v>90731</v>
+        <v>90732</v>
       </c>
       <c r="AO44" s="7">
-        <v>264396</v>
+        <v>264397</v>
       </c>
       <c r="AP44" s="9">
         <f t="shared" si="15"/>
-        <v>0.8667698238896393</v>
+        <v>0.86677310219121673</v>
       </c>
       <c r="AQ44" s="4">
         <v>305678</v>
@@ -8557,14 +8557,14 @@
       </c>
       <c r="O45" s="10">
         <f t="shared" si="4"/>
-        <v>66784</v>
+        <v>66785</v>
       </c>
       <c r="P45" s="7">
-        <v>218606</v>
+        <v>218607</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="5"/>
-        <v>0.86550582794881536</v>
+        <v>0.86550978715317373</v>
       </c>
       <c r="R45" s="4">
         <v>256692</v>
@@ -8625,14 +8625,14 @@
       </c>
       <c r="AI45" s="10">
         <f t="shared" si="12"/>
-        <v>74819</v>
+        <v>74820</v>
       </c>
       <c r="AJ45" s="7">
-        <v>232248</v>
+        <v>232249</v>
       </c>
       <c r="AK45" s="9">
         <f t="shared" si="13"/>
-        <v>0.89502404735479102</v>
+        <v>0.89502790109754593</v>
       </c>
       <c r="AL45" s="4">
         <v>264815</v>
@@ -9135,15 +9135,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>4591886</v>
+        <v>4591902</v>
       </c>
       <c r="F48" s="13">
         <f>SUM(F10:F47)</f>
-        <v>8024204</v>
+        <v>8024220</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.91000088684272418</v>
+        <v>0.91000270135469197</v>
       </c>
       <c r="H48" s="13">
         <f>SUM(H10:H47)</f>
@@ -9155,15 +9155,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>2452800</v>
+        <v>2452814</v>
       </c>
       <c r="K48" s="13">
         <f>SUM(K10:K47)</f>
-        <v>8179240</v>
+        <v>8179254</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.89661948526409263</v>
+        <v>0.89662101996325716</v>
       </c>
       <c r="M48" s="13">
         <f>SUM(M10:M47)</f>
@@ -9175,15 +9175,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2507213</v>
+        <v>2507228</v>
       </c>
       <c r="P48" s="13">
         <f>SUM(P10:P47)</f>
-        <v>8297536</v>
+        <v>8297551</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.89060795066069465</v>
+        <v>0.89060956067109531</v>
       </c>
       <c r="R48" s="13">
         <f>SUM(R10:R47)</f>
@@ -9195,15 +9195,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>2026686</v>
+        <v>2026696</v>
       </c>
       <c r="U48" s="13">
         <f>SUM(U10:U47)</f>
-        <v>8410336</v>
+        <v>8410346</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.88807661693706696</v>
+        <v>0.88807767287183215</v>
       </c>
       <c r="W48" s="13">
         <f>SUM(W10:W47)</f>
@@ -9215,15 +9215,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>2872148</v>
+        <v>2872158</v>
       </c>
       <c r="Z48" s="13">
         <f>SUM(Z10:Z47)</f>
-        <v>8522388</v>
+        <v>8522398</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.8863386406189403</v>
+        <v>0.88633968063101276</v>
       </c>
       <c r="AB48" s="13">
         <f>SUM(AB10:AB47)</f>
@@ -9235,15 +9235,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>2248023</v>
+        <v>2248032</v>
       </c>
       <c r="AE48" s="13">
         <f>SUM(AE10:AE47)</f>
-        <v>8617277</v>
+        <v>8617286</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.89231269931291957</v>
+        <v>0.89231363125630425</v>
       </c>
       <c r="AG48" s="13">
         <f>SUM(AG10:AG47)</f>
@@ -9255,15 +9255,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2832605</v>
+        <v>2832621</v>
       </c>
       <c r="AJ48" s="13">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8715270</v>
+        <v>8715286</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.89317176734103576</v>
+        <v>0.89317340707775961</v>
       </c>
       <c r="AL48" s="13">
         <f>SUM(AL10:AL47)</f>
@@ -9275,15 +9275,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2422713</v>
+        <v>2422732</v>
       </c>
       <c r="AO48" s="13">
         <f>SUM(AO10:AO47)</f>
-        <v>8713074</v>
+        <v>8713093</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.88487743794967733</v>
+        <v>0.88487936754092389</v>
       </c>
       <c r="AQ48" s="13">
         <f>SUM(AQ10:AQ47)</f>
@@ -9295,15 +9295,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>2607088</v>
+        <v>2607107</v>
       </c>
       <c r="AT48" s="13">
         <f>SUM(AT10:AT47)</f>
-        <v>8806544</v>
+        <v>8806563</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.88937049768849652</v>
+        <v>0.88937241649335985</v>
       </c>
       <c r="AV48" s="13">
         <f>SUM(AV10:AV47)</f>
@@ -9315,15 +9315,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>3160769</v>
+        <v>3160793</v>
       </c>
       <c r="AY48" s="13">
         <f>SUM(AY10:AY47)</f>
-        <v>8886770</v>
+        <v>8886794</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.8911151802446674</v>
+        <v>0.89111758682932374</v>
       </c>
       <c r="BA48" s="13">
         <f>SUM(BA10:BA47)</f>
@@ -9335,15 +9335,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2003765</v>
+        <v>2003788</v>
       </c>
       <c r="BD48" s="13">
         <f>SUM(BD10:BD47)</f>
-        <v>8967019</v>
+        <v>8967042</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.89186061303426611</v>
+        <v>0.89186290061658302</v>
       </c>
       <c r="BF48" s="13">
         <f>SUM(BF10:BF47)</f>
@@ -9355,15 +9355,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>3828602</v>
+        <v>3828630</v>
       </c>
       <c r="BI48" s="13">
         <f>SUM(BI10:BI47)</f>
-        <v>9043429</v>
+        <v>9043457</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.88879101261938842</v>
+        <v>0.88879376446809022</v>
       </c>
     </row>
     <row r="49" spans="1:62" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
